--- a/chore/init-metadonnees-ig/ig/ValueSet-MeltingPotVS.xlsx
+++ b/chore/init-metadonnees-ig/ig/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:03:16+00:00</t>
+    <t>2026-07-01T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
